--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Data + Applied AI)</t>
+          <t>Scientist III, Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PLUME</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>26.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5030a1bb6b9395c</t>
+          <t>https://www.indeed.com/viewjob?jk=242e2f2f15e944fd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>React JS and Node JS Developer</t>
+          <t>Senior Data Engineer (Data + Applied AI)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>PLUME</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Kinesis, Redshift, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4302a48fbfa72b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b5030a1bb6b9395c</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3725a0e179d8a789</t>
+          <t>https://www.indeed.com/viewjob?jk=f4302a48fbfa72b9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Technical Architect - Data (Oracle)</t>
+          <t>React JS and Node JS Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9e7a6323a73ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=3725a0e179d8a789</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
+          <t>Associate Technical Architect - Data (Oracle)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba561a7b1076cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9e7a6323a73ddf</t>
         </is>
       </c>
     </row>
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff197f6507571237</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba561a7b1076cd7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
+          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9e5db8b8f70d82</t>
+          <t>https://www.indeed.com/viewjob?jk=ff197f6507571237</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
+          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87d23704eafca584</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9e5db8b8f70d82</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL Database Administrator (DBA)</t>
+          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a6a1cc72921a57</t>
+          <t>https://www.indeed.com/viewjob?jk=87d23704eafca584</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>Multi-Cloud SQL Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a279b4dc75fa05b2</t>
+          <t>https://www.indeed.com/viewjob?jk=18a6a1cc72921a57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>Senior Cloud Software Engineer (Full-Stack)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c9dd79e5f8809c1</t>
+          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer 2026 - US,UK</t>
+          <t>Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
+          <t>https://www.indeed.com/viewjob?jk=a279b4dc75fa05b2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49b45df7b2ac405</t>
+          <t>https://www.indeed.com/viewjob?jk=7c9dd79e5f8809c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer</t>
+          <t>Senior Analytics Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,46 +937,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
+          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, EMR, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda14dafda45f1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a49b45df7b2ac405</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DataOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
+          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9633aa99c845fd92</t>
+          <t>https://www.indeed.com/viewjob?jk=eda14dafda45f1a6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Revenue Intelligence</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbd118d6be25a868</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
         </is>
       </c>
     </row>
@@ -1133,25 +1133,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
+          <t>https://www.indeed.com/viewjob?jk=9633aa99c845fd92</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Data Engineer, Revenue Intelligence</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=fbd118d6be25a868</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
+          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
+          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Senior Application Developer / Engineer / Programmer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
+          <t>https://www.indeed.com/viewjob?jk=fe599190cd4853ee</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Loenbro</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Knowledge Platform</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a97391e031fbe7e</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d04492e99eca232</t>
+          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Knowledge Platform</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e71d288565747ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Knowledge Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Airwallex</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016b24c707be3d95</t>
+          <t>https://www.indeed.com/viewjob?jk=4a97391e031fbe7e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer 4 - Contingent (contract)</t>
+          <t>Senior Data Engineer - Knowledge Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Airwallex</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, NoSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38b2018ce77fd05</t>
+          <t>https://www.indeed.com/viewjob?jk=1e71d288565747ae</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>AI Engineer / Senior AI Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Blue Matter</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
+          <t>Sr DevOps Infrastructure Service Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
+          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
+          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c6c22bfb3d302d</t>
+          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2-6 Month Senior Data Engineer Contract</t>
+          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tripledot Studios</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, GCP, Spark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
+          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
+          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c6c22bfb3d302d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>2-6 Month Senior Data Engineer Contract</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Tripledot Studios</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, GCP, Spark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,29 +2376,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
+          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61859efe066d7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c1455f57f98249</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Architect - Paid Relocation to Cincinnati</t>
+          <t>QA Automation Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
+          <t>https://www.indeed.com/viewjob?jk=e32c84fbc1c2464a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
+          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=61859efe066d7fac</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer Specialist</t>
+          <t>Data Architect - Paid Relocation to Cincinnati</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SAMYANG AMERICA INC</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,89 +2701,89 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d09ed4f454c71e</t>
+          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0551e51d2fda9</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c7db9666c539fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+          <t>https://www.indeed.com/viewjob?jk=12c7db9666c539fb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bad294f816f723</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,137 +2981,137 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Sr. Data Engineer Specialist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>SAMYANG AMERICA INC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=73d09ed4f454c71e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0551e51d2fda9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,172 +3121,172 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b4138e7fb03c99</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Multi Cloud Linux Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Oracle, PostgreSQL, MySQL, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b706c6d89269a3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Associate, Data &amp; Analytics</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Palm Tree</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc699288e8c88f76</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Developer – AI Projects</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>General Property Construction</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55e25e3c6cd3752</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b2ffe5d9c2ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full-Stack Platform Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Social Impact</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Power BI, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35a4a7eaaadb3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,40 +3471,1510 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64203283044db188</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Zoom Communications</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Java API Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Java API Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Corning</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Principle AI &amp; Data Scientist</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Alignment Healthcare</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Orange, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, MLOps, MLflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=066c6d8069347b46</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Payabli</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Cloud Software Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TRC</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Opiniion</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Nicklaus Children's Health System</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2b4138e7fb03c99</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Multi Cloud Linux Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Oracle, PostgreSQL, MySQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b706c6d89269a3d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Devops Engineer-5</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Brandt Information Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Full Stack Developer – AI Projects</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>General Property Construction</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Doral, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e55e25e3c6cd3752</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6b2ffe5d9c2ef14</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Analytics, Finance &amp; StrategyNew</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, ETL, ELT, dbt, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09dd1bf805dee945</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64203283044db188</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
           <t>Advisor IT Systems</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Occidental</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Houston, TX, US USA</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D130" t="n">
         <v>10.4</v>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35a0fb08c802d618</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,235 +643,235 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
+          <t>Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba561a7b1076cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=a279b4dc75fa05b2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
+          <t>Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff197f6507571237</t>
+          <t>https://www.indeed.com/viewjob?jk=7c9dd79e5f8809c1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
+          <t>Senior Analytics Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9e5db8b8f70d82</t>
+          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
+          <t>Senior Cloud Software Engineer (Full-Stack)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87d23704eafca584</t>
+          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL Database Administrator (DBA)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, EMR, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a6a1cc72921a57</t>
+          <t>https://www.indeed.com/viewjob?jk=a49b45df7b2ac405</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (Full-Stack)</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5093e8180b857d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a279b4dc75fa05b2</t>
+          <t>https://www.indeed.com/viewjob?jk=090066a47b6dd531</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>Senior DataOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c9dd79e5f8809c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer 2026 - US,UK</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
+          <t>https://www.indeed.com/viewjob?jk=eda14dafda45f1a6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49b45df7b2ac405</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
+          <t>https://www.indeed.com/viewjob?jk=9633aa99c845fd92</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer, Revenue Intelligence</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda14dafda45f1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=fbd118d6be25a868</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9633aa99c845fd92</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Revenue Intelligence</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbd118d6be25a868</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
+          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Application Developer / Engineer / Programmer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
+          <t>https://www.indeed.com/viewjob?jk=fe599190cd4853ee</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Loenbro</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Columbus, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
+          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Application Developer / Engineer / Programmer</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, Scala</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe599190cd4853ee</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Senior Data Engineer - Knowledge Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Airwallex</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
+          <t>https://www.indeed.com/viewjob?jk=4a97391e031fbe7e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Senior Python and SAS Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Spatial Front</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Specialist Data Engineering</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Knowledge Platform</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a97391e031fbe7e</t>
+          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Knowledge Platform</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e71d288565747ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Python and SAS Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Spatial Front</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Specialist Data Engineering</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
+          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>AI Engineer / Senior AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hurrdat</t>
+          <t>Blue Matter</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca56751aee18003</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Senior AWS Python Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,77 +1781,77 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd25943628391ab</t>
+          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ddfff990a5f81c</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>AEP Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
+          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>Sr DevOps Infrastructure Service Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AWS Python Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
+          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
+          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AEP Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr DevOps Infrastructure Service Engineer</t>
+          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
+          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
+          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c6c22bfb3d302d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Engineer - (Java, Microservices, Data/Systems Engineering) *HYBRID*</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
+          <t>https://www.indeed.com/viewjob?jk=55bc9fe56fb418d8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>2-6 Month Senior Data Engineer Contract</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>Tripledot Studios</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2267,38 +2267,38 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, GCP, Spark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c6c22bfb3d302d</t>
+          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2-6 Month Senior Data Engineer Contract</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tripledot Studios</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, GCP, Spark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
+          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
+          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>QA Automation Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e32c84fbc1c2464a</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QA Automation Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e32c84fbc1c2464a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=61859efe066d7fac</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Architect - Paid Relocation to Cincinnati</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
+          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61859efe066d7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Architect - Paid Relocation to Cincinnati</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,104 +2691,104 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c7db9666c539fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0551e51d2fda9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>TNT Crane &amp; Rigging</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Talend, dbt, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=46e05984bc6ba0ca</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=12c7db9666c539fb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer Specialist</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SAMYANG AMERICA INC</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d09ed4f454c71e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0551e51d2fda9</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Principle AI &amp; Data Scientist</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, MLOps, MLflow, Git, Python</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=066c6d8069347b46</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Principle AI &amp; Data Scientist</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, MLOps, MLflow, Git, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+          <t>https://www.indeed.com/viewjob?jk=066c6d8069347b46</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Analytics, Finance &amp; StrategyNew</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, GCP, Scala, ETL, ELT, dbt, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b4138e7fb03c99</t>
+          <t>https://www.indeed.com/viewjob?jk=09dd1bf805dee945</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Multi Cloud Linux Engineer</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Oracle, PostgreSQL, MySQL, Terraform</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b706c6d89269a3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Full Stack Developer – AI Projects</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>General Property Construction</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
+          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Full Stack Developer – AI Projects</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>General Property Construction</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
+          <t>https://www.indeed.com/viewjob?jk=e55e25e3c6cd3752</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55e25e3c6cd3752</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b2ffe5d9c2ef14</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b2ffe5d9c2ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=64203283044db188</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Analytics, Finance &amp; StrategyNew</t>
+          <t>Advisor IT Systems</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Occidental</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, ETL, ELT, dbt, Airflow, Git, Python</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4905,76 +4905,6 @@
         </is>
       </c>
       <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=09dd1bf805dee945</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64203283044db188</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Advisor IT Systems</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Occidental</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35a0fb08c802d618</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,35 +643,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a279b4dc75fa05b2</t>
+          <t>https://www.indeed.com/viewjob?jk=7518086fa359e2be</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c9dd79e5f8809c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a279b4dc75fa05b2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer 2026 - US,UK</t>
+          <t>Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
+          <t>https://www.indeed.com/viewjob?jk=7c9dd79e5f8809c1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (Full-Stack)</t>
+          <t>Senior Analytics Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,59 +766,59 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
+          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Cloud Software Engineer (Full-Stack)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49b45df7b2ac405</t>
+          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, EMR, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5093e8180b857d</t>
+          <t>https://www.indeed.com/viewjob?jk=a49b45df7b2ac405</t>
         </is>
       </c>
     </row>
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=090066a47b6dd531</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5093e8180b857d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
+          <t>https://www.indeed.com/viewjob?jk=090066a47b6dd531</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DataOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda14dafda45f1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
+          <t>https://www.indeed.com/viewjob?jk=eda14dafda45f1a6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9633aa99c845fd92</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Revenue Intelligence</t>
+          <t>Platform Engineer (AWS)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbd118d6be25a868</t>
+          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=9633aa99c845fd92</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>Senior Data Engineer, Revenue Intelligence</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbd118d6be25a868</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
+          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Application Developer / Engineer / Programmer</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, Scala</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe599190cd4853ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Senior Application Developer / Engineer / Programmer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
+          <t>https://www.indeed.com/viewjob?jk=fe599190cd4853ee</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Loenbro</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Knowledge Platform</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a97391e031fbe7e</t>
+          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Python and SAS Developer</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Spatial Front</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Specialist Data Engineering</t>
+          <t>Senior Data Engineer - Knowledge Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Airwallex</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
+          <t>https://www.indeed.com/viewjob?jk=4a97391e031fbe7e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Python and SAS Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Spatial Front</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
+          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Specialist Data Engineering</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
+          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AWS Python Developer</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,42 +1781,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
+          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer / Senior AI Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Blue Matter</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AEP Engineer</t>
+          <t>Senior AWS Python Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr DevOps Infrastructure Service Engineer</t>
+          <t>AEP Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
+          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
+          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr DevOps Infrastructure Service Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
+          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
+          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
+          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
+          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c6c22bfb3d302d</t>
+          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Engineer - (Java, Microservices, Data/Systems Engineering) *HYBRID*</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55bc9fe56fb418d8</t>
+          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c6c22bfb3d302d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>Sr Engineer - (Java, Microservices, Data/Systems Engineering) *HYBRID*</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=55bc9fe56fb418d8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2-6 Month Senior Data Engineer Contract</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tripledot Studios</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, GCP, Spark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>2-6 Month Senior Data Engineer Contract</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>Tripledot Studios</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
+          <t>AWS, Redshift, GCP, Spark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
+          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
+          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>QA Automation Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e32c84fbc1c2464a</t>
+          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c1455f57f98249</t>
+          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61859efe066d7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Architect - Paid Relocation to Cincinnati</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,322 +2691,322 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0551e51d2fda9</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TNT Crane &amp; Rigging</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Talend, dbt, Power BI</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e05984bc6ba0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c7db9666c539fb</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,627 +3016,627 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c1455f57f98249</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>QA Automation Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e32c84fbc1c2464a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,129 +3786,129 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=61859efe066d7fac</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Data Architect - Paid Relocation to Cincinnati</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0551e51d2fda9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TNT Crane &amp; Rigging</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Talend, dbt, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=46e05984bc6ba0ca</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=12c7db9666c539fb</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,19 +4381,19 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4402,11 +4402,11 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Dev Ops. Architect</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Principle AI &amp; Data Scientist</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, MLOps, MLflow, Git, Python</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=066c6d8069347b46</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Analytics, Finance &amp; StrategyNew</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, ETL, ELT, dbt, Airflow, Git, Python</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,67 +4661,67 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09dd1bf805dee945</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Full Stack Developer – AI Projects</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>General Property Construction</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55e25e3c6cd3752</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b2ffe5d9c2ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,40 +4871,1440 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64203283044db188</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Corning</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Payabli</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior Cloud Software Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>TRC</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Opiniion</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Nicklaus Children's Health System</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Application Modernization Architect</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Sparc technology services inc</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Oracle, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=448c12afca90484e</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Software Development Specialist Advisor</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b65a93ab1aa85d6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Dev Ops. Architect</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Dev Ops. Architect</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Principle AI &amp; Data Scientist</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Alignment Healthcare</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Orange, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, MLOps, MLflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=066c6d8069347b46</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Analytics, Finance &amp; StrategyNew</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, ETL, ELT, dbt, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09dd1bf805dee945</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Devops Engineer-5</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Brandt Information Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Full Stack Developer – AI Projects</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>General Property Construction</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Doral, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e55e25e3c6cd3752</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6b2ffe5d9c2ef14</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64203283044db188</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
           <t>Advisor IT Systems</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>Occidental</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>Houston, TX, US USA</t>
         </is>
       </c>
-      <c r="D128" t="n">
+      <c r="D168" t="n">
         <v>10.4</v>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E168" t="inlineStr">
         <is>
           <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35a0fb08c802d618</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G168"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Columbus, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Loenbro</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Knowledge Platform</t>
+          <t>Senior Python and SAS Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Spatial Front</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a97391e031fbe7e</t>
+          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Python and SAS Developer</t>
+          <t>Specialist Data Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Spatial Front</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
+          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Specialist Data Engineering</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
+          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>AI Engineer / Senior AI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Blue Matter</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>Senior AWS Python Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,69 +1816,69 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AWS Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AEP Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
+          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AEP Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Sr DevOps Infrastructure Service Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr DevOps Infrastructure Service Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
+          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
+          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
+          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
+          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
+          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c6c22bfb3d302d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Sr Engineer - (Java, Microservices, Data/Systems Engineering) *HYBRID*</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c6c22bfb3d302d</t>
+          <t>https://www.indeed.com/viewjob?jk=55bc9fe56fb418d8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Engineer - (Java, Microservices, Data/Systems Engineering) *HYBRID*</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55bc9fe56fb418d8</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>2-6 Month Senior Data Engineer Contract</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>Tripledot Studios</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, GCP, Spark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2-6 Month Senior Data Engineer Contract</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tripledot Studios</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, GCP, Spark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
+          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c1455f57f98249</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>QA Automation Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c1455f57f98249</t>
+          <t>https://www.indeed.com/viewjob?jk=e32c84fbc1c2464a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>QA Automation Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e32c84fbc1c2464a</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=61859efe066d7fac</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Architect - Paid Relocation to Cincinnati</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61859efe066d7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Architect - Paid Relocation to Cincinnati</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,69 +3846,69 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0551e51d2fda9</t>
         </is>
       </c>
     </row>
@@ -4061,29 +4061,29 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0551e51d2fda9</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TNT Crane &amp; Rigging</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Talend, dbt, Power BI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=46e05984bc6ba0ca</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TNT Crane &amp; Rigging</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Talend, dbt, Power BI</t>
+          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e05984bc6ba0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=12c7db9666c539fb</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c7db9666c539fb</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,32 +5501,32 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Application Modernization Architect</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>Sparc technology services inc</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>Azure, Data Factory, Oracle, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+          <t>https://www.indeed.com/viewjob?jk=448c12afca90484e</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Application Modernization Architect</t>
+          <t>Software Development Specialist Advisor</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Sparc technology services inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Oracle, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,14 +5886,14 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448c12afca90484e</t>
+          <t>https://www.indeed.com/viewjob?jk=b65a93ab1aa85d6b</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Software Development Specialist Advisor</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65a93ab1aa85d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Dev Ops. Architect</t>
+          <t>Principle AI &amp; Data Scientist</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, MLOps, MLflow, Git, Python</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=066c6d8069347b46</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Principle AI &amp; Data Scientist</t>
+          <t>Analytics, Finance &amp; StrategyNew</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, MLOps, MLflow, Git, Python</t>
+          <t>AWS, RDS, GCP, Scala, ETL, ELT, dbt, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=066c6d8069347b46</t>
+          <t>https://www.indeed.com/viewjob?jk=09dd1bf805dee945</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Analytics, Finance &amp; StrategyNew</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, ETL, ELT, dbt, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09dd1bf805dee945</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
@@ -6103,17 +6103,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Full Stack Developer – AI Projects</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>General Property Construction</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
+          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Full Stack Developer – AI Projects</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>General Property Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
+          <t>https://www.indeed.com/viewjob?jk=64203283044db188</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Advisor IT Systems</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Occidental</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6200,111 +6200,6 @@
         </is>
       </c>
       <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e55e25e3c6cd3752</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b2ffe5d9c2ef14</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64203283044db188</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Advisor IT Systems</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Occidental</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35a0fb08c802d618</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior DataOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5093e8180b857d</t>
+          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=090066a47b6dd531</t>
+          <t>https://www.indeed.com/viewjob?jk=eda14dafda45f1a6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Platform Engineer (AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda14dafda45f1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
+          <t>https://www.indeed.com/viewjob?jk=9633aa99c845fd92</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Platform Engineer (AWS)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9633aa99c845fd92</t>
+          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Revenue Intelligence</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbd118d6be25a868</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
+          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Software Engineer III - Fullstack - AWS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=07dc72c0e4f9dd7e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
+          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Loenbro</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Columbus, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
+          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Application Developer / Engineer / Programmer</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, Scala</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe599190cd4853ee</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
+          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Python and SAS Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>Spatial Front</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Specialist Data Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Python and SAS Developer</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Spatial Front</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
+          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Specialist Data Engineering</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
+          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Engineer / Senior AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Matter</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior AWS Python Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,94 +1756,94 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>AEP Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AWS Python Developer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
+          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr DevOps Infrastructure Service Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,19 +1861,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
+          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AEP Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr DevOps Infrastructure Service Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
+          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
+          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
+          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>2-6 Month Senior Data Engineer Contract</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Tripledot Studios</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, GCP, Spark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
+          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c6c22bfb3d302d</t>
+          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Engineer - (Java, Microservices, Data/Systems Engineering) *HYBRID*</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55bc9fe56fb418d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2-6 Month Senior Data Engineer Contract</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tripledot Studios</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, GCP, Spark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
+          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Data Architect - Paid Relocation to Cincinnati</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
+          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c1455f57f98249</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>QA Automation Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e32c84fbc1c2464a</t>
+          <t>https://www.indeed.com/viewjob?jk=61859efe066d7fac</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,67 +3681,67 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
+          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61859efe066d7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,129 +3751,129 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Architect - Paid Relocation to Cincinnati</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c0551e51d2fda9</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0551e51d2fda9</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TNT Crane &amp; Rigging</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Talend, dbt, Power BI</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e05984bc6ba0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Kafka, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c7db9666c539fb</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,32 +5396,32 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,32 +5431,32 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,32 +5466,32 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,24 +5561,24 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,14 +5606,14 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Full Stack Developer – AI Projects</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>General Property Construction</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,462 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Opiniion</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Nicklaus Children's Health System</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Application Modernization Architect</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Sparc technology services inc</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Oracle, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=448c12afca90484e</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Software Development Specialist Advisor</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b65a93ab1aa85d6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Principle AI &amp; Data Scientist</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Alignment Healthcare</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Orange, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, MLOps, MLflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=066c6d8069347b46</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Analytics, Finance &amp; StrategyNew</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, ETL, ELT, dbt, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=09dd1bf805dee945</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Devops Engineer-5</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Full Stack Developer – AI Projects</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>General Property Construction</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=64203283044db188</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Advisor IT Systems</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Occidental</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35a0fb08c802d618</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5053,17 +5053,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
         </is>
       </c>
     </row>
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
@@ -5543,17 +5543,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Dev Ops. Architect</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,17 +5596,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Full Stack Developer – AI Projects</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>General Property Construction</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Full Stack Developer – AI Projects</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Property Construction</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,15 +5736,50 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Java Compliance &amp; Governance Developer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=64203283044db188</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G153"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,35 +643,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
+          <t>Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7518086fa359e2be</t>
+          <t>https://www.indeed.com/viewjob?jk=a279b4dc75fa05b2</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a279b4dc75fa05b2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c9dd79e5f8809c1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>Senior Analytics Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c9dd79e5f8809c1</t>
+          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer 2026 - US,UK</t>
+          <t>Senior Cloud Software Engineer (Full-Stack)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,77 +766,77 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
+          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (Full-Stack)</t>
+          <t>Senior DataOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49b45df7b2ac405</t>
+          <t>https://www.indeed.com/viewjob?jk=eda14dafda45f1a6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Platform Engineer (AWS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda14dafda45f1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
+          <t>https://www.indeed.com/viewjob?jk=9633aa99c845fd92</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Platform Engineer (AWS)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9633aa99c845fd92</t>
+          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Software Engineer III - Fullstack - AWS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
+          <t>https://www.indeed.com/viewjob?jk=07dc72c0e4f9dd7e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
+          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack - AWS</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Loenbro</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07dc72c0e4f9dd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Columbus, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
+          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
+          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Senior Python and SAS Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Spatial Front</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Specialist Data Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Python and SAS Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spatial Front</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Specialist Data Engineering</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
+          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Engineer / Senior AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Matter</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior AWS Python Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
+          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AWS Python Developer</t>
+          <t>AEP Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
+          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
+          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AEP Engineer</t>
+          <t>Sr DevOps Infrastructure Service Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr DevOps Infrastructure Service Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
+          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
+          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
+          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
+          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>2-6 Month Senior Data Engineer Contract</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tripledot Studios</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, GCP, Spark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2-6 Month Senior Data Engineer Contract</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tripledot Studios</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, GCP, Spark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
+          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect - Paid Relocation to Cincinnati</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Architect - Paid Relocation to Cincinnati</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,42 +3531,42 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,67 +3576,67 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61859efe066d7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
         </is>
       </c>
     </row>
@@ -3658,12 +3658,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c0551e51d2fda9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
         </is>
       </c>
     </row>
@@ -5053,17 +5053,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,42 +5071,42 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,59 +5186,59 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,19 +5396,19 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Wecom Fiber</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>Full Stack Developer – AI Projects</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>General Property Construction</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,192 +5596,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Full Stack Developer – AI Projects</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>General Property Construction</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Java Compliance &amp; Governance Developer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64203283044db188</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Convey Health Solutions</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
+          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Architect - Paid Relocation to Cincinnati</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
+          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect - Paid Relocation to Cincinnati</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,69 +3496,69 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
         </is>
       </c>
     </row>
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,69 +5036,69 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Wecom Fiber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Dev Ops. Architect</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Full Stack Developer – AI Projects</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>General Property Construction</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5570,41 +5570,6 @@
         </is>
       </c>
       <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Full Stack Developer – AI Projects</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>General Property Construction</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, Snowflake, DynamoDB</t>
+          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eda14dafda45f1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Platform Engineer (AWS)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
+          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Platform Engineer (AWS)</t>
+          <t>Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=9633aa99c845fd92</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9633aa99c845fd92</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
+          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Software Engineer III - Fullstack - AWS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,69 +1116,69 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
+          <t>https://www.indeed.com/viewjob?jk=07dc72c0e4f9dd7e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack - AWS</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07dc72c0e4f9dd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Loenbro</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Columbus, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
+          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
         </is>
       </c>
     </row>
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Senior Python and SAS Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Spatial Front</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Python and SAS Developer</t>
+          <t>Specialist Data Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spatial Front</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
+          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist Data Engineering</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
+          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Engineer / Senior AI Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Matter</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>Senior AWS Python Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,69 +1606,69 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AWS Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AEP Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
+          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AEP Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Sr DevOps Infrastructure Service Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr DevOps Infrastructure Service Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
+          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
+          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
+          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
+          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
+          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2-6 Month Senior Data Engineer Contract</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tripledot Studios</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, GCP, Spark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Webster University</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Hadoop, Spark, Scala, Power BI, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
+          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Data Architect - Paid Relocation to Cincinnati</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect - Paid Relocation to Cincinnati</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,42 +3426,42 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,42 +3471,42 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, SQL Server, ETL, ELT, Jenkins, Azure DevOps</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153db5113e33b494</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,42 +4931,42 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Wecom Fiber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Dev Ops. Architect</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Dev Ops. Architect</t>
+          <t>Full Stack Developer – AI Projects</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>General Property Construction</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5500,76 +5500,6 @@
         </is>
       </c>
       <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Full Stack Developer – AI Projects</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>General Property Construction</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer | The Points Guy</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9633aa99c845fd92</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
+          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Software Engineer III - Fullstack - AWS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,69 +1081,69 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
+          <t>https://www.indeed.com/viewjob?jk=07dc72c0e4f9dd7e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack - AWS</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07dc72c0e4f9dd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Loenbro</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Columbus, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
+          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
         </is>
       </c>
     </row>
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Senior Python and SAS Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Spatial Front</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Python and SAS Developer</t>
+          <t>Specialist Data Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spatial Front</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
+          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Specialist Data Engineering</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
+          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Engineer / Senior AI Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Matter</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>Senior AWS Python Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,69 +1571,69 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AWS Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AEP Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
+          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AEP Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Sr DevOps Infrastructure Service Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr DevOps Infrastructure Service Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
+          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
+          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
+          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,19 +1861,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
+          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
+          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect - Paid Relocation to Cincinnati</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Architect - Paid Relocation to Cincinnati</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,69 +3391,69 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,69 +4896,69 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,17 +5036,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Wecom Fiber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,17 +5351,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Dev Ops. Architect</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Full Stack Developer – AI Projects</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>General Property Construction</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5465,41 +5465,6 @@
         </is>
       </c>
       <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Full Stack Developer – AI Projects</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>General Property Construction</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,52 +1063,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack - AWS</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07dc72c0e4f9dd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Loenbro</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Columbus, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
+          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
         </is>
       </c>
     </row>
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Senior Python and SAS Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Spatial Front</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Python and SAS Developer</t>
+          <t>Specialist Data Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Spatial Front</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
+          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Specialist Data Engineering</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
+          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Engineer / Senior AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Matter</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>Senior AWS Python Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,69 +1536,69 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AWS Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AEP Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
+          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AEP Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Sr DevOps Infrastructure Service Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr DevOps Infrastructure Service Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
+          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
+          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
+          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
+          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
+          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Architect - Paid Relocation to Cincinnati</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
+          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Architect - Paid Relocation to Cincinnati</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,69 +3356,69 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
         </is>
       </c>
     </row>
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,69 +4861,69 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Wecom Fiber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Dev Ops. Architect</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Dev Ops. Architect</t>
+          <t>Full Stack Developer – AI Projects</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>General Property Construction</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,52 +5421,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Full Stack Developer – AI Projects</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>General Property Construction</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
+          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer I (Full Stack) Java</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
         </is>
       </c>
     </row>
@@ -3268,17 +3268,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Architect - Paid Relocation to Cincinnati</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Total Quality Logistics (TQL)</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,69 +3321,69 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
         </is>
       </c>
     </row>
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,69 +4826,69 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,17 +4966,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,17 +5246,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Dev Ops. Architect</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Full Stack Developer – AI Projects</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>General Property Construction</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
+          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Full Stack Developer – AI Projects</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>General Property Construction</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,50 +5386,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Wecom Fiber</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>React JS and Node JS Developer</t>
+          <t>Associate Technical Architect - Data (Oracle)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4302a48fbfa72b9</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9e7a6323a73ddf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>React JS and Node JS Developer</t>
+          <t>Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3725a0e179d8a789</t>
+          <t>https://www.indeed.com/viewjob?jk=a279b4dc75fa05b2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Technical Architect - Data (Oracle)</t>
+          <t>Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9e7a6323a73ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=7c9dd79e5f8809c1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>Senior Analytics Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a279b4dc75fa05b2</t>
+          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>Senior Cloud Software Engineer (Full-Stack)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,29 +696,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c9dd79e5f8809c1</t>
+          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer 2026 - US,UK</t>
+          <t>Senior DataOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,108 +727,108 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
+          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (Full-Stack)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer</t>
+          <t>Platform Engineer (AWS)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
+          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Platform Engineer (AWS)</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
+          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Loenbro</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Columbus, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
+          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
+          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Senior Python and SAS Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Spatial Front</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Specialist Data Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Python and SAS Developer</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Spatial Front</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
+          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Specialist Data Engineering</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
+          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
+          <t>Software Engineer I (Full Stack) Java</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer I (Full Stack) Java</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,24 +3216,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
+          <t>https://www.indeed.com/viewjob?jk=594f058d7c8a610d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,69 +3286,69 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Spark, Scala, Kafka, Data Modeling, Terraform, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca84caf988e212bb</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Oracle, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb518870b55148fc</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,42 +4686,42 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,94 +4766,94 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>Full Stack Developer – AI Projects</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>General Property Construction</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Dev Ops. Architect</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,155 +5246,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Full Stack Developer – AI Projects</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>General Property Construction</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Wecom Fiber</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Technical Architect - Data (Oracle)</t>
+          <t>Data &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Parker's Kitchen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9e7a6323a73ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=a279b4dc75fa05b2</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>Parker Management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a279b4dc75fa05b2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c9dd79e5f8809c1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>Senior Analytics Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c9dd79e5f8809c1</t>
+          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer 2026 - US,UK</t>
+          <t>Senior Cloud Software Engineer (Full-Stack)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,104 +661,104 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
+          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (Full-Stack)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer</t>
+          <t>Platform Engineer (AWS)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
+          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Platform Engineer (AWS)</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
+          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Loenbro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
+          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Senior Python and SAS Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Spatial Front</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
+          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
+          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Senior Software Engineer, Integrations</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Python and SAS Developer</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Spatial Front</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
+          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Specialist Data Engineering</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
+          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1296,29 +1296,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>AI Engineer / Senior AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Blue Matter</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>Senior AWS Python Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,94 +1361,94 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
+          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AEP Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
+          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,15 +1458,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
+          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>Sr DevOps Infrastructure Service Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AWS Python Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
+          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
+          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AEP Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Software Engineer I (Full Stack) Java</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr DevOps Infrastructure Service Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
+          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,94 +1791,94 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer I (Full Stack) Java</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
+          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,182 +3076,182 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Associate, AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,59 +3261,59 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594f058d7c8a610d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,42 +4511,42 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,67 +4591,67 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,59 +4661,59 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Full Stack Developer – AI Projects</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>General Property Construction</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5080,181 +5080,6 @@
         </is>
       </c>
       <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Full Stack Developer – AI Projects</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>General Property Construction</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Wecom Fiber</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, ETL, ELT, AKS</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,59 +3041,59 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Senior Associate, AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Hadoop, Hive, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaa5de4e613b797</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Associate, AWS Cloud Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,42 +4406,42 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,19 +4696,19 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nicklaus Children's Health System</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a24af3f7388e80</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4905,181 +4905,6 @@
         </is>
       </c>
       <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Full Stack Developer – AI Projects</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>General Property Construction</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Wecom Fiber</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>Senior Cloud Software Engineer (Full-Stack)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Parker Management</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,77 +591,77 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c9dd79e5f8809c1</t>
+          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer 2026 - US,UK</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (Full-Stack)</t>
+          <t>Platform Engineer (AWS)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
+          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Platform Engineer (AWS)</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Loenbro</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
+          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Engineer Analytics</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ddf2924330606</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Python and SAS Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>Spatial Front</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Python and SAS Developer</t>
+          <t>AI Engineer / Senior AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Spatial Front</t>
+          <t>Blue Matter</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
+          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Spark, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d290ee24e1a475</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Senior AWS Python Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
+          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AEP Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
+          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AWS Python Developer</t>
+          <t>Sr DevOps Infrastructure Service Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
+          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
+          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AEP Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,29 +1431,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr DevOps Infrastructure Service Engineer</t>
+          <t>Software Engineer I (Full Stack) Java</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer I (Full Stack) Java</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97576904d3410017</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,147 +2831,147 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Associate, AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,94 +2981,94 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Associate, AWS Cloud Platform Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,67 +4241,67 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,59 +4381,59 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Scala, Kafka, MongoDB, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,24 +4511,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,295 +4616,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior Cloud Software Engineer</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>TRC</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Route</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Lehi, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Opiniion</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, BigQuery, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9da27a923ccab2</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Devops Engineer-5</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Wecom Fiber</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,87 +818,87 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Snowflake, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
+          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>AI Engineer / Senior AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Blue Matter</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fca2dbc1cb62ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer Analytics</t>
+          <t>Senior AWS Python Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a961bf8d8ee3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Python and SAS Developer</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spatial Front</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,24 +976,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, Spark, PySpark, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cace19948d1122ec</t>
+          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,29 +1016,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
+          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,59 +1046,59 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>AEP Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,50 +1108,50 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Sr DevOps Infrastructure Service Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
+          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
+          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AWS Python Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
+          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, MySQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
+          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AEP Engineer</t>
+          <t>Software Engineer I (Full Stack) Java</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
         </is>
       </c>
     </row>
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr DevOps Infrastructure Service Engineer</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer I (Full Stack) Java</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,147 +2621,147 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Associate, AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,94 +2771,94 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Associate, AWS Cloud Platform Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76952bdd1db77c87</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,67 +3996,67 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Devops Engineer-5</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,24 +4266,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,295 +4336,15 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Payabli</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Cloud Software Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>TRC</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Route</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Lehi, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Devops Engineer-5</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0dfec438fe5f230</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Wecom Fiber</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data &amp; Integration Engineer</t>
+          <t>Senior Cloud Software Engineer (Full-Stack)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Parker's Kitchen</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,77 +556,77 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, BigQuery, Cloud Storage, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a279b4dc75fa05b2</t>
+          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (Full-Stack)</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5093e8180b857d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EMR, Lambda, Redshift, S3, GCP, BigQuery, Hadoop, HDFS, Hive, MapReduce</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
+          <t>https://www.indeed.com/viewjob?jk=090066a47b6dd531</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Software Engineer III - Fullstack - AWS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=07dc72c0e4f9dd7e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Application Developer / Engineer / Programmer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
+          <t>https://www.indeed.com/viewjob?jk=fe599190cd4853ee</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,29 +841,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
+          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AWS Python Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Engineer / Senior AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Matter</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior AWS Python Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
+          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Sr Engineer - (Java, Microservices, Data/Systems Engineering) *HYBRID*</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=55bc9fe56fb418d8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,104 +2621,104 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c1455f57f98249</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Associate, AWS Cloud Platform Engineer</t>
+          <t>Senior Data Engineer (Azure/Databricks)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Acuity Analytics</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
+          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI &amp; Data Analytics Architect</t>
+          <t>Senior Associate, AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Oracle, SQL Server, Azure Cosmos DB, ETL, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
+          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>TNT Crane &amp; Rigging</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Talend, dbt, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=46e05984bc6ba0ca</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,59 +3996,59 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Devops Engineer-5</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Dev Ops. Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Dev Ops. Architect</t>
+          <t>Application Modernization Architect</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Sparc technology services inc</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Azure, Data Factory, Oracle, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=448c12afca90484e</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
+          <t>Software Development Specialist Advisor</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Wecom Fiber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,17 +4336,227 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b65a93ab1aa85d6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Dev Ops. Architect</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Dev Ops. Architect</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Principle AI &amp; Data Scientist</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Alignment Healthcare</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Orange, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, MLOps, MLflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=066c6d8069347b46</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Wecom Fiber</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
           <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Analytics, Finance &amp; StrategyNew</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, ETL, ELT, dbt, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09dd1bf805dee945</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Devops Engineer-5</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-11.xlsx
+++ b/results/job_matches_2026-04-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (Full-Stack)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e68aed4fb5428da</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Cloud Software Engineer (Full-Stack)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5093e8180b857d</t>
+          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Platform Engineer (AWS)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=090066a47b6dd531</t>
+          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Platform Engineer (AWS)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,112 +661,112 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, DataOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8d1d9d043cd2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5b89f5da184cb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
+          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack - AWS</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07dc72c0e4f9dd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Application Developer / Engineer / Programmer</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, Scala</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe599190cd4853ee</t>
+          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -902,116 +902,116 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
+          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr DevOps Infrastructure Service Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242643709c670116</t>
+          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
+          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer / Senior AI Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blue Matter</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Vertex AI, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9a41c33498321d</t>
+          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AWS Python Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Inframark</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582daf0783444929</t>
+          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AEP Engineer</t>
+          <t>Guidewire ETL Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Data Modeling, Splunk, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d5599d0190e3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Software Engineer I (Full Stack) Java</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr DevOps Infrastructure Service Engineer</t>
+          <t>DATA ENGINEER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>The GEO Group, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdee34709275ca25</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172a54e6b4658010</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b3c5652baa523f</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Inframark</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455a057972235895</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer I (Full Stack) Java</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,94 +1301,94 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Engineer - (Java, Microservices, Data/Systems Engineering) *HYBRID*</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55bc9fe56fb418d8</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DATA ENGINEER</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The GEO Group, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d58843bcd42732</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Fullstack Engineer (Retool)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Parser Limited</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,112 +2376,112 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Associate, AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Leo Facilities Maintenance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,102 +2526,102 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,94 +2631,94 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c1455f57f98249</t>
+          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure/Databricks)</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Acuity Analytics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08c52b8be54d813</t>
+          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Associate, AWS Cloud Platform Engineer</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
+          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TNT Crane &amp; Rigging</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Talend, dbt, Power BI</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e05984bc6ba0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Leo Facilities Maintenance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d81fef551c0c0fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a97d79e2b95510</t>
+          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f2f52dcabb706</t>
+          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af446c2579eebba8</t>
+          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262957346bbab6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5313aeebd075c192</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa0a2ad309b3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10762058cac0b75</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1dd856c64ff5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1896dd1fe34f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0371a3c7e8f847e</t>
+          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafd5eda62e911f4</t>
+          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4535bf8a7108211</t>
+          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a68eb49385697644</t>
+          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21035efae6c4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe39d24dc97733a</t>
+          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15c0a06509d0f024</t>
+          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa688b190a64e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c15d4ca64690c2</t>
+          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9471107e8b93804c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92d98461c7cbf82</t>
+          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e17e778b2b9f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0137f329fef2c34</t>
+          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b803af10fd336f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbca3457bf1681d</t>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c025d5b4f4d0f043</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683adfb225dcd666</t>
+          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31fb13e57f7d26a</t>
+          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68413893cdcaa348</t>
+          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe2fd846e5e89685</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,602 +3961,77 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13484b9c7b6b160c</t>
+          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d45b16a298a0a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Claude/Codex/Gemini)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcb0ec8dcb159a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Corning</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Databricks Lakehouse, Power BI, Tableau, MLflow</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e443192de143d</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Azure Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Azure Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Payabli</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6aec507f41a1cbd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Cloud Software Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>TRC</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, RDS, Scala, Oracle, SQL Server, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3338ef100e8fb177</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Route</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Lehi, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Snowflake, DynamoDB, Data Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Application Modernization Architect</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Sparc technology services inc</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Oracle, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=448c12afca90484e</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Software Development Specialist Advisor</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b65a93ab1aa85d6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Principle AI &amp; Data Scientist</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Alignment Healthcare</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Orange, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, MLOps, MLflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=066c6d8069347b46</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Wecom Fiber</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Analytics, Finance &amp; StrategyNew</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, ETL, ELT, dbt, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=09dd1bf805dee945</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Devops Engineer-5</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4c25ae4a2245b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b1cef4b777b5a5</t>
         </is>
       </c>
     </row>
